--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:12:38+00:00</t>
+    <t>2026-09-14T19:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1798,7 +1798,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="81691-8"/&gt;
-  &lt;display value="DNA mismatch repair protein Mlh1 [Presence] in Cancer specimen by Immune stain"/&gt;
+  &lt;display value="MLH-1 Ag [Presence] in Cancer specimen by Immune stain"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -1880,7 +1880,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="81692-6"/&gt;
-  &lt;display value="DNA mismatch repair protein Msh2 [Presence] in Cancer specimen by Immune stain"/&gt;
+  &lt;display value="MSH-2 Ag [Presence] in Cancer specimen by Immune stain"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -1944,7 +1944,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="81693-4"/&gt;
-  &lt;display value="DNA mismatch repair protein Msh6 [Presence] in Cancer specimen by Immune stain"/&gt;
+  &lt;display value="MSH-6 Ag [Presence] in Cancer specimen by Immune stain"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -2008,7 +2008,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="81694-2"/&gt;
-  &lt;display value="Mismatch repair endonuclease PMS2 [Presence] in Cancer specimen by Immune stain"/&gt;
+  &lt;display value="PMS2 Ag [Presence] in Cancer specimen by Immune stain"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -2072,7 +2072,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="96271-2"/&gt;
-  &lt;display value="DNA mismatch repair protein Msh3 [Presence] in Cancer specimen by Immune stain"/&gt;
+  &lt;display value="DNA mismatch repair protein Msh3 Ag [Presence] in Cancer specimen by Immune stain"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -2136,7 +2136,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="96272-0"/&gt;
-  &lt;display value="DNA mismatch repair protein Mlh3 [Presence] in Cancer specimen by Immune stain"/&gt;
+  &lt;display value="DNA mismatch repair protein Mlh3 Ag [Presence] in Cancer specimen by Immune stain"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:45:33+00:00</t>
+    <t>2026-09-14T20:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:15:28+00:00</t>
+    <t>2026-09-14T20:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:43:02+00:00</t>
+    <t>2026-09-14T21:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:08:50+00:00</t>
+    <t>2026-09-14T21:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:38:27+00:00</t>
+    <t>2026-09-14T22:18:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-immunohistochemistry-mmr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:18:02+00:00</t>
+    <t>2026-09-14T22:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
